--- a/output/quickfixclose11_portfolio_daily.xlsx
+++ b/output/quickfixclose11_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>163,215.35</t>
+          <t>161,439.96</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+63.22%</t>
+          <t>+61.44%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>168,871  (+68.87%)</t>
+          <t>167,233  (+67.23%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,700  (5.7 pts of return)</t>
+          <t>3,890  (5.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.0x</t>
+          <t>2.9x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.4%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,253  (-1.27%)</t>
+          <t>-1,263  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5747,22 +5747,70 @@
         <v>46234</v>
       </c>
       <c r="B186" s="5" t="n">
-        <v>163215.35</v>
+        <v>163370.03</v>
       </c>
       <c r="C186" s="5" t="n">
+        <v>6437.43</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>156932.6</v>
+      </c>
+      <c r="E186" t="n">
+        <v>4</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>163370.03</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>6437.43</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>156932.6</v>
+      </c>
+      <c r="E187" t="n">
+        <v>4</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Natural_Gas_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>161439.96</v>
+      </c>
+      <c r="C188" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="D186" s="5" t="n">
-        <v>163215.35</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D188" s="5" t="n">
+        <v>161439.96</v>
+      </c>
+      <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-1,839); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9908,7 @@
         <v>-30.96</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>183011.14</v>
+        <v>180275.61</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9884,14 +9932,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.04</v>
+        <v>-1.16</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>175714.83</v>
@@ -9900,14 +9956,14 @@
         <v>2442.44</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>-97.7</v>
+        <v>-2833.23</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>183042.1</v>
+        <v>180306.58</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose11_portfolio_daily.xlsx
+++ b/output/quickfixclose11_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>161,439.96</t>
+          <t>161,431.51</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+61.44%</t>
+          <t>+61.43%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,890  (5.8 pts of return)</t>
+          <t>3,899  (5.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5795,22 +5795,82 @@
         <v>46238</v>
       </c>
       <c r="B188" s="5" t="n">
-        <v>161439.96</v>
+        <v>161531.23</v>
       </c>
       <c r="C188" s="5" t="n">
-        <v>0</v>
+        <v>4852.25</v>
       </c>
       <c r="D188" s="5" t="n">
-        <v>161439.96</v>
+        <v>156678.98</v>
       </c>
       <c r="E188" t="n">
-        <v>0</v>
-      </c>
-      <c r="F188" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); NY_Natural_Gas_Futures stop (-1,839); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>NY_Natural_Gas_Futures stop (-1,839)</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>161531.23</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>9505.780000000001</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>152025.45</v>
+      </c>
+      <c r="E189" t="n">
+        <v>6</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 1,567); Nasdaq_100_E_mini short (risk 1,551); S_P_500_E_mini short (risk 1,536)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>161431.51</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>161431.51</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,520)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9822,7 +9882,7 @@
         <v>-48.06</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>183202.6</v>
+        <v>180369.37</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9865,7 +9925,7 @@
         <v>-62.79</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>183139.8</v>
+        <v>180306.58</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9908,7 +9968,7 @@
         <v>-30.96</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>180275.61</v>
+        <v>180262.71</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9959,11 +10019,183 @@
         <v>-2833.23</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>180306.58</v>
+        <v>180417.43</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
           <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>172881.6</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>2403.05</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>-8.34</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>180294.16</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>170478.55</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>2369.65</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>180302.51</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>168108.9</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>2336.71</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>180293.67</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>165772.18</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>2304.23</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>-3.94</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>180302.64</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfixclose11_portfolio_daily.xlsx
+++ b/output/quickfixclose11_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>161,431.51</t>
+          <t>159,893.54</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+61.43%</t>
+          <t>+59.89%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>167,233  (+67.23%)</t>
+          <t>165,659  (+65.66%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>3,899  (5.8 pts of return)</t>
+          <t>3,916  (5.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,263  (-1.27%)</t>
+          <t>-1,267  (-1.27%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5851,26 +5851,54 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>161431.51</v>
+        <v>161531.23</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>11026.03</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>150505.2</v>
+      </c>
+      <c r="E190" t="n">
+        <v>7</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Gold_Futures_COMEX, NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini, US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 1,520)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>159893.54</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>159893.54</v>
+      </c>
+      <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>161431.51</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 1,520)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 1,505); NY_Palladium_Futures short (risk 1,490)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX stop (-1,531); Nasdaq_100_E_mini open_at_end (open-&gt;closed 0); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M85"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9968,7 +9996,7 @@
         <v>-30.96</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>180262.71</v>
+        <v>177931.73</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -10062,7 +10090,7 @@
         <v>-8.34</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>180294.16</v>
+        <v>177963.18</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -10105,7 +10133,7 @@
         <v>-0.13</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>180302.51</v>
+        <v>177986.46</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -10148,7 +10176,7 @@
         <v>-0.49</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>180293.67</v>
+        <v>177962.69</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -10172,14 +10200,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
       <c r="F85" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H85" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I85" s="5" t="n">
         <v>165772.18</v>
@@ -10188,12 +10224,98 @@
         <v>2304.23</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>-3.94</v>
+        <v>-2319.99</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>180302.64</v>
+        <v>177986.59</v>
       </c>
       <c r="M85" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>163467.95</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>2272.2</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>-6.14</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>177980.31</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>161195.75</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>2240.62</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>177971.53</v>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
